--- a/data/trans_camb/DCD-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,8</t>
+          <t>-4,49; 1,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 10,29</t>
+          <t>3,31; 10,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -0,79</t>
+          <t>-9,23; -0,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 9,77</t>
+          <t>0,31; 10,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; -0,76</t>
+          <t>-5,6; -0,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,4</t>
+          <t>3,71; 9,31</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 29,73</t>
+          <t>-43,88; 17,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 148,32</t>
+          <t>31,56; 134,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,02; -4,82</t>
+          <t>-42,35; -4,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 56,8</t>
+          <t>2,33; 63,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,4; -6,12</t>
+          <t>-37,8; -3,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,86; 76,42</t>
+          <t>25,45; 78,35</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,65</t>
+          <t>-1,9; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 6,38</t>
+          <t>-3,09; 6,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -0,59</t>
+          <t>-6,59; -0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 13,38</t>
+          <t>6,58; 13,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,39</t>
+          <t>-3,6; 0,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 8,45</t>
+          <t>-1,15; 8,42</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 50,87</t>
+          <t>-25,05; 46,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 104,24</t>
+          <t>-36,75; 105,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,85; -3,92</t>
+          <t>-37,49; -1,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,52; 93,83</t>
+          <t>36,52; 89,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 3,83</t>
+          <t>-28,87; 3,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 79,24</t>
+          <t>-5,62; 79,34</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,79</t>
+          <t>-2,36; 2,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 9,2</t>
+          <t>3,53; 9,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; -0,72</t>
+          <t>-7,23; -0,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 13,54</t>
+          <t>-5,95; 13,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,27</t>
+          <t>-3,8; 0,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 10,02</t>
+          <t>1,06; 10,28</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,24; 69,42</t>
+          <t>-35,42; 60,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,21; 217,32</t>
+          <t>49,33; 225,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,5; -4,75</t>
+          <t>-43,64; -0,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 96,77</t>
+          <t>-34,42; 97,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 3,47</t>
+          <t>-34,07; 4,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,19; 107,45</t>
+          <t>11,32; 111,25</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,12</t>
+          <t>-1,57; 3,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,89</t>
+          <t>5,12; 10,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,06</t>
+          <t>-4,31; 2,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,56</t>
+          <t>3,98; 13,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,66</t>
+          <t>-2,4; 1,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 11,22</t>
+          <t>6,09; 11,08</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 62,58</t>
+          <t>-20,87; 67,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>66,27; 201,62</t>
+          <t>65,36; 201,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 15,11</t>
+          <t>-25,37; 16,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,68; 87,44</t>
+          <t>24,69; 94,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 15,45</t>
+          <t>-19,02; 14,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,49; 107,99</t>
+          <t>48,78; 105,7</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,27</t>
+          <t>-1,14; 1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,39</t>
+          <t>3,17; 7,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,64</t>
+          <t>-4,89; -1,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,33</t>
+          <t>3,34; 10,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,52</t>
+          <t>-2,7; -0,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,52</t>
+          <t>4,33; 8,54</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 21,11</t>
+          <t>-15,52; 22,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43,17; 120,6</t>
+          <t>47,99; 122,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,28; -10,49</t>
+          <t>-28,61; -8,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,95; 66,58</t>
+          <t>20,81; 66,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -5,09</t>
+          <t>-22,25; -4,52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,12; 76,38</t>
+          <t>36,65; 77,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DCD-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,55</t>
+          <t>7,04</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,15</t>
+          <t>-4,48; 1,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,04</t>
+          <t>2,92; 9,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; -0,82</t>
+          <t>-9,1; -1,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 10,61</t>
+          <t>3,61; 11,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -0,37</t>
+          <t>-5,88; -0,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,31</t>
+          <t>4,55; 9,81</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,88; 17,6</t>
+          <t>-44,12; 18,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,56; 134,19</t>
+          <t>27,33; 135,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,35; -4,57</t>
+          <t>-44,78; -5,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 63,61</t>
+          <t>17,06; 69,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -3,06</t>
+          <t>-38,54; -5,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,45; 78,35</t>
+          <t>30,54; 84,14</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>7,36</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,53</t>
+          <t>-1,98; 2,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,19</t>
+          <t>2,23; 7,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -0,25</t>
+          <t>-6,78; -0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 13,02</t>
+          <t>6,22; 12,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,36</t>
+          <t>-3,59; 0,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 8,42</t>
+          <t>5,27; 9,52</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 46,33</t>
+          <t>-26,09; 45,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 105,98</t>
+          <t>28,24; 140,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,49; -1,41</t>
+          <t>-37,9; -2,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,52; 89,89</t>
+          <t>34,4; 88,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 3,5</t>
+          <t>-29,31; 4,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 79,34</t>
+          <t>42,29; 92,94</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>9,68</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,47</t>
+          <t>-2,36; 2,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,49</t>
+          <t>3,53; 9,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -0,15</t>
+          <t>-7,38; -0,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 13,7</t>
+          <t>9,03; 16,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,4</t>
+          <t>-3,95; 0,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,28</t>
+          <t>7,29; 12,46</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>115,61%</t>
+          <t>116,15%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 60,42</t>
+          <t>-35,8; 68,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49,33; 225,74</t>
+          <t>48,99; 218,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -0,27</t>
+          <t>-44,39; -1,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 97,54</t>
+          <t>53,74; 133,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 4,94</t>
+          <t>-35,89; 4,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,32; 111,25</t>
+          <t>63,74; 137,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,97</t>
+          <t>7,66</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>10,98</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,83</t>
+          <t>9,47</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,45</t>
+          <t>-1,69; 3,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 10,52</t>
+          <t>4,81; 10,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,33</t>
+          <t>-4,42; 1,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 13,32</t>
+          <t>7,58; 13,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,59</t>
+          <t>-2,22; 1,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,08</t>
+          <t>7,24; 11,65</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>124,12%</t>
+          <t>119,29%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 67,72</t>
+          <t>-21,76; 57,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65,36; 201,66</t>
+          <t>58,52; 188,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 16,1</t>
+          <t>-25,98; 13,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,69; 94,27</t>
+          <t>42,43; 97,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 14,87</t>
+          <t>-17,49; 16,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,78; 105,7</t>
+          <t>56,95; 111,26</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>10,4</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>8,41</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,35</t>
+          <t>-1,08; 1,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,52</t>
+          <t>4,95; 7,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -1,35</t>
+          <t>-5,02; -1,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,44</t>
+          <t>8,45; 12,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,54</t>
+          <t>-2,7; -0,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,54</t>
+          <t>7,32; 9,51</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 22,46</t>
+          <t>-14,89; 21,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47,99; 122,91</t>
+          <t>68,58; 129,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,61; -8,96</t>
+          <t>-29,02; -10,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,81; 66,42</t>
+          <t>47,92; 78,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -4,52</t>
+          <t>-22,21; -5,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,65; 77,53</t>
+          <t>60,05; 85,97</t>
         </is>
       </c>
     </row>
